--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.85038994700667</v>
+        <v>6.638188366388584</v>
       </c>
       <c r="D2" t="n">
-        <v>41.65240971403055</v>
+        <v>6.768516578529964</v>
       </c>
       <c r="E2" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F2" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.19356777962644</v>
+        <v>2.631454764189296</v>
       </c>
       <c r="D3" t="n">
-        <v>17.18597961818539</v>
+        <v>2.792721687955126</v>
       </c>
       <c r="E3" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F3" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.2433062625098</v>
+        <v>2.639537267657842</v>
       </c>
       <c r="D4" t="n">
-        <v>16.46431908852005</v>
+        <v>2.675451851884508</v>
       </c>
       <c r="E4" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F4" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.21594671857405</v>
+        <v>5.560091341768283</v>
       </c>
       <c r="D5" t="n">
-        <v>35.16721610967724</v>
+        <v>5.714672617822552</v>
       </c>
       <c r="E5" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F5" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.37894744547646</v>
+        <v>2.174078959889925</v>
       </c>
       <c r="D6" t="n">
-        <v>12.37867410220793</v>
+        <v>2.01153454160879</v>
       </c>
       <c r="E6" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F6" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.66397501634988</v>
+        <v>4.820395940156856</v>
       </c>
       <c r="D7" t="n">
-        <v>29.73447069212694</v>
+        <v>4.831851487470628</v>
       </c>
       <c r="E7" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F7" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.14486495980001</v>
+        <v>6.848540555967502</v>
       </c>
       <c r="D8" t="n">
-        <v>42.04132616531167</v>
+        <v>6.831715501863146</v>
       </c>
       <c r="E8" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F8" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.53918557824427</v>
+        <v>4.150117656464694</v>
       </c>
       <c r="D9" t="n">
-        <v>25.65729671873038</v>
+        <v>4.169310716793686</v>
       </c>
       <c r="E9" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F9" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.84919775580529</v>
+        <v>3.71299463531836</v>
       </c>
       <c r="D10" t="n">
-        <v>22.16155752907765</v>
+        <v>3.601253098475119</v>
       </c>
       <c r="E10" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F10" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.52532730534955</v>
+        <v>2.522865687119302</v>
       </c>
       <c r="D11" t="n">
-        <v>28.70543118083398</v>
+        <v>4.664632566885521</v>
       </c>
       <c r="E11" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F11" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.65397073901934</v>
+        <v>4.331270245090643</v>
       </c>
       <c r="D12" t="n">
-        <v>25.44973048255145</v>
+        <v>4.135581203414611</v>
       </c>
       <c r="E12" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F12" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.67586415293554</v>
+        <v>4.172327924852024</v>
       </c>
       <c r="D13" t="n">
-        <v>31.03328883960592</v>
+        <v>5.042909436435963</v>
       </c>
       <c r="E13" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F13" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.85137216105769</v>
+        <v>1.763347976171875</v>
       </c>
       <c r="D14" t="n">
-        <v>14.93829321073147</v>
+        <v>2.427472646743865</v>
       </c>
       <c r="E14" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F14" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>25.98557292037257</v>
+        <v>4.222655599560542</v>
       </c>
       <c r="D15" t="n">
-        <v>41.39444121622191</v>
+        <v>6.726596697636062</v>
       </c>
       <c r="E15" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F15" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>25.32597235882487</v>
+        <v>4.115470508309042</v>
       </c>
       <c r="D16" t="n">
-        <v>24.98125220941052</v>
+        <v>4.05945348402921</v>
       </c>
       <c r="E16" t="n">
-        <v>9.089458566979612</v>
+        <v>1.477037017134187</v>
       </c>
       <c r="F16" t="n">
-        <v>9.447147273223628</v>
+        <v>1.535161431898839</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
